--- a/data/trans_orig/Q23_tabaco_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la edad, en cuartiles, de inicio en el consumo de tabaco en 2007</t>
+          <t>Población según la edad, en cuartiles, de inicio en el consumo de tabaco en 2007 (tasa de respuesta: 86,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15887</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35031</t>
+          <t>35644</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20713</t>
+          <t>20784</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40658</t>
+          <t>40224</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41403</t>
+          <t>42123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69461</t>
+          <t>69637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102193</t>
+          <t>102206</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>137294</t>
+          <t>137099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50615</t>
+          <t>50918</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75471</t>
+          <t>76556</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>163269</t>
+          <t>161002</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>207340</t>
+          <t>206545</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,68%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66275</t>
+          <t>65061</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>97601</t>
+          <t>94164</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28399</t>
+          <t>28160</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50164</t>
+          <t>49739</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>100701</t>
+          <t>98571</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>137641</t>
+          <t>137473</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,08%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>126211</t>
+          <t>128022</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>164734</t>
+          <t>166107</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36376</t>
+          <t>37284</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61375</t>
+          <t>60812</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>171867</t>
+          <t>172019</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>214976</t>
+          <t>216577</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54074</t>
+          <t>54167</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>86620</t>
+          <t>88214</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50674</t>
+          <t>51287</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>78237</t>
+          <t>80226</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>113185</t>
+          <t>112427</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>157973</t>
+          <t>155975</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>147350</t>
+          <t>149145</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191008</t>
+          <t>195677</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88235</t>
+          <t>87416</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>120422</t>
+          <t>120067</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>246235</t>
+          <t>250906</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>298167</t>
+          <t>304941</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>38,34%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89574</t>
+          <t>88552</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>125416</t>
+          <t>126330</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37580</t>
+          <t>36342</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61532</t>
+          <t>60605</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133287</t>
+          <t>133384</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>179096</t>
+          <t>178644</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>149756</t>
+          <t>149576</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>192410</t>
+          <t>192403</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49465</t>
+          <t>47746</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75725</t>
+          <t>75172</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>209117</t>
+          <t>204357</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>263389</t>
+          <t>260444</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24723</t>
+          <t>25194</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47879</t>
+          <t>48384</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36381</t>
+          <t>36377</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59703</t>
+          <t>59938</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67317</t>
+          <t>66051</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>101745</t>
+          <t>99232</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94245</t>
+          <t>93081</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>130033</t>
+          <t>130878</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51009</t>
+          <t>51183</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>76053</t>
+          <t>76613</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>154506</t>
+          <t>154165</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>198521</t>
+          <t>197773</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,58%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61475</t>
+          <t>59191</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92483</t>
+          <t>90206</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22037</t>
+          <t>22212</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41499</t>
+          <t>42314</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88365</t>
+          <t>88742</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124137</t>
+          <t>125899</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107078</t>
+          <t>106666</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143667</t>
+          <t>145608</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39020</t>
+          <t>38423</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63351</t>
+          <t>61795</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>152960</t>
+          <t>154934</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>197743</t>
+          <t>202638</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>37,48%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45249</t>
+          <t>43277</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73513</t>
+          <t>72596</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58405</t>
+          <t>60170</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>90357</t>
+          <t>92545</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>109839</t>
+          <t>111678</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>154604</t>
+          <t>153564</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>133322</t>
+          <t>133443</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>173414</t>
+          <t>172938</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>93416</t>
+          <t>94240</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>127881</t>
+          <t>127821</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>237282</t>
+          <t>236140</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>291126</t>
+          <t>288482</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>97130</t>
+          <t>97919</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>132623</t>
+          <t>132929</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48939</t>
+          <t>48537</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>77953</t>
+          <t>76239</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>151964</t>
+          <t>152612</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>198657</t>
+          <t>200601</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>142946</t>
+          <t>146065</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>184547</t>
+          <t>185527</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>84224</t>
+          <t>84640</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>118710</t>
+          <t>118799</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>241296</t>
+          <t>242129</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>294367</t>
+          <t>293664</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>161377</t>
+          <t>159419</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>216836</t>
+          <t>215021</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>191561</t>
+          <t>189889</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>243760</t>
+          <t>243171</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>368854</t>
+          <t>367237</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>448405</t>
+          <t>441739</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>511314</t>
+          <t>513862</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>590367</t>
+          <t>591289</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>311032</t>
+          <t>308552</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>372441</t>
+          <t>369448</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>845909</t>
+          <t>844605</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>946060</t>
+          <t>942683</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,66%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>341400</t>
+          <t>340382</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>408477</t>
+          <t>408777</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>156441</t>
+          <t>154881</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>204338</t>
+          <t>205037</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>515594</t>
+          <t>511341</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>598091</t>
+          <t>592782</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>568525</t>
+          <t>572225</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>647867</t>
+          <t>650850</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>236687</t>
+          <t>234941</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>292305</t>
+          <t>292311</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>816937</t>
+          <t>820550</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>916984</t>
+          <t>919160</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la edad, en cuartiles, de inicio en el consumo de tabaco en 2012</t>
+          <t>Población según la edad, en cuartiles, de inicio en el consumo de tabaco en 2012 (tasa de respuesta: 94,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51050</t>
+          <t>51366</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80683</t>
+          <t>82293</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36674</t>
+          <t>36060</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62368</t>
+          <t>62160</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93974</t>
+          <t>93198</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>134657</t>
+          <t>134839</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>104003</t>
+          <t>102345</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>140957</t>
+          <t>138958</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63800</t>
+          <t>64058</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>93525</t>
+          <t>93120</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>176762</t>
+          <t>175718</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>224016</t>
+          <t>222299</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66813</t>
+          <t>67859</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100728</t>
+          <t>99404</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35777</t>
+          <t>35073</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61015</t>
+          <t>60710</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>107854</t>
+          <t>108990</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>148445</t>
+          <t>150367</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>153310</t>
+          <t>154318</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>192999</t>
+          <t>195050</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34818</t>
+          <t>35354</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62045</t>
+          <t>62019</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>198576</t>
+          <t>196289</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>246025</t>
+          <t>246641</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,3%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87079</t>
+          <t>89258</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>129663</t>
+          <t>130611</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75645</t>
+          <t>76671</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>110737</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>174419</t>
+          <t>175462</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>229693</t>
+          <t>229868</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>148854</t>
+          <t>147245</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>194126</t>
+          <t>192903</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>107002</t>
+          <t>107114</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>144690</t>
+          <t>144015</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>266010</t>
+          <t>264320</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>326076</t>
+          <t>324717</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113568</t>
+          <t>114711</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>155977</t>
+          <t>158939</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42344</t>
+          <t>41251</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70866</t>
+          <t>70100</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163431</t>
+          <t>163184</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>212710</t>
+          <t>216041</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>187115</t>
+          <t>187774</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>235526</t>
+          <t>236477</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>88838</t>
+          <t>88398</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>124521</t>
+          <t>124953</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>289429</t>
+          <t>288916</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>347200</t>
+          <t>348961</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62067</t>
+          <t>63126</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98967</t>
+          <t>99860</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59769</t>
+          <t>59410</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>90796</t>
+          <t>92658</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>130935</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>180643</t>
+          <t>180926</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>121255</t>
+          <t>121647</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>163272</t>
+          <t>164819</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72083</t>
+          <t>71899</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>105249</t>
+          <t>104546</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>205996</t>
+          <t>203684</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>258660</t>
+          <t>257007</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54674</t>
+          <t>54678</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85221</t>
+          <t>85467</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53207</t>
+          <t>52477</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85991</t>
+          <t>84597</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114810</t>
+          <t>115871</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159706</t>
+          <t>159540</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>142933</t>
+          <t>140090</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>183968</t>
+          <t>186096</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75420</t>
+          <t>75870</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110094</t>
+          <t>109818</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>229459</t>
+          <t>229154</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>285236</t>
+          <t>283735</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65388</t>
+          <t>64952</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>100772</t>
+          <t>100618</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>74614</t>
+          <t>74270</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>109270</t>
+          <t>107753</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>148109</t>
+          <t>147666</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>199087</t>
+          <t>197895</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>143393</t>
+          <t>147598</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>187285</t>
+          <t>190623</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>105698</t>
+          <t>105117</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>143320</t>
+          <t>143452</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>263989</t>
+          <t>262848</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>320833</t>
+          <t>319318</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75283</t>
+          <t>74010</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>109241</t>
+          <t>110034</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>51373</t>
+          <t>51437</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>80954</t>
+          <t>80273</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>133888</t>
+          <t>132300</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>179651</t>
+          <t>178394</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>164214</t>
+          <t>163478</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>208245</t>
+          <t>209228</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>99062</t>
+          <t>99272</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>137548</t>
+          <t>137946</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>278191</t>
+          <t>274290</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>334244</t>
+          <t>334724</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>304148</t>
+          <t>296710</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>375622</t>
+          <t>370892</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>273655</t>
+          <t>272069</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>339613</t>
+          <t>337775</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>595870</t>
+          <t>594325</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>686919</t>
+          <t>692506</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>558339</t>
+          <t>554835</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>641444</t>
+          <t>641369</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>379072</t>
+          <t>380444</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>449377</t>
+          <t>450557</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>963085</t>
+          <t>960857</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1076940</t>
+          <t>1071043</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>339945</t>
+          <t>340351</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>411809</t>
+          <t>411138</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>204267</t>
+          <t>205790</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>260608</t>
+          <t>261481</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>564245</t>
+          <t>564998</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>656086</t>
+          <t>656947</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>687193</t>
+          <t>689918</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>775790</t>
+          <t>780342</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>331091</t>
+          <t>331337</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>401390</t>
+          <t>402629</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1036339</t>
+          <t>1041138</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1150041</t>
+          <t>1156243</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la edad, en cuartiles, de inicio en el consumo de tabaco en 2016</t>
+          <t>Población según la edad, en cuartiles, de inicio en el consumo de tabaco en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50148</t>
+          <t>50848</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79729</t>
+          <t>80910</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46378</t>
+          <t>46618</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74681</t>
+          <t>73313</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>105191</t>
+          <t>106004</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>145009</t>
+          <t>145898</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,25%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81513</t>
+          <t>80952</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>115655</t>
+          <t>115435</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62947</t>
+          <t>62164</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91418</t>
+          <t>91344</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>151967</t>
+          <t>151947</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>196378</t>
+          <t>196251</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45645</t>
+          <t>44671</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72582</t>
+          <t>73210</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21982</t>
+          <t>22035</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41744</t>
+          <t>42770</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>72807</t>
+          <t>72471</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>106832</t>
+          <t>106234</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>138197</t>
+          <t>138385</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>178067</t>
+          <t>177533</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45706</t>
+          <t>44860</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72243</t>
+          <t>71514</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,47 +7276,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
+          <t>31,85%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>216260</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>193616</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>241212</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>35,95%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>32,18%</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>216260</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>191168</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>240386</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>35,95%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>31,78%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,1%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78323</t>
+          <t>79397</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>115148</t>
+          <t>117146</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62251</t>
+          <t>63883</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95235</t>
+          <t>94371</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>148586</t>
+          <t>151949</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>199161</t>
+          <t>200405</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98095</t>
+          <t>100186</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138018</t>
+          <t>140456</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89326</t>
+          <t>88648</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>124274</t>
+          <t>124049</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>196473</t>
+          <t>197617</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>248995</t>
+          <t>248786</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90944</t>
+          <t>89431</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127629</t>
+          <t>128114</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58470</t>
+          <t>56566</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88183</t>
+          <t>86291</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>154477</t>
+          <t>157401</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>203632</t>
+          <t>203637</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>176349</t>
+          <t>179353</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>223161</t>
+          <t>224542</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>85995</t>
+          <t>87708</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>121186</t>
+          <t>122807</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>279181</t>
+          <t>276150</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>336105</t>
+          <t>334882</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,05%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51930</t>
+          <t>50925</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>82791</t>
+          <t>82078</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51649</t>
+          <t>52132</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81534</t>
+          <t>80586</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111917</t>
+          <t>111987</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>154859</t>
+          <t>153967</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>97149</t>
+          <t>98386</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>134946</t>
+          <t>136872</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>79931</t>
+          <t>79621</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>113720</t>
+          <t>111230</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>184851</t>
+          <t>188925</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>236180</t>
+          <t>236363</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95554</t>
+          <t>95380</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132723</t>
+          <t>134717</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53573</t>
+          <t>52885</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82488</t>
+          <t>82022</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>157284</t>
+          <t>155637</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>203589</t>
+          <t>206051</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113186</t>
+          <t>114634</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>153315</t>
+          <t>154095</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52719</t>
+          <t>53171</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82156</t>
+          <t>81100</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>178190</t>
+          <t>176837</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>226147</t>
+          <t>226097</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48712</t>
+          <t>49832</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79192</t>
+          <t>80159</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79891</t>
+          <t>79363</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>114387</t>
+          <t>112552</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>137143</t>
+          <t>137928</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>183845</t>
+          <t>184383</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>121291</t>
+          <t>122300</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>160156</t>
+          <t>160280</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>88459</t>
+          <t>88583</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>123079</t>
+          <t>121611</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>219270</t>
+          <t>218659</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>271133</t>
+          <t>272476</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,65%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>76103</t>
+          <t>75350</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>108920</t>
+          <t>110335</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>58197</t>
+          <t>57064</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>89545</t>
+          <t>88642</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>141624</t>
+          <t>140937</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>187858</t>
+          <t>189147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>127805</t>
+          <t>126893</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>167897</t>
+          <t>168044</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>77628</t>
+          <t>78041</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>112136</t>
+          <t>111330</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>218334</t>
+          <t>216843</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>272391</t>
+          <t>270505</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>261058</t>
+          <t>260349</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>324836</t>
+          <t>325449</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>268577</t>
+          <t>267788</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>332033</t>
+          <t>330423</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>547265</t>
+          <t>549075</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>637074</t>
+          <t>632826</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>433280</t>
+          <t>435364</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>508938</t>
+          <t>511439</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>348060</t>
+          <t>350950</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>415691</t>
+          <t>417655</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>806206</t>
+          <t>807519</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>907659</t>
+          <t>903699</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>335886</t>
+          <t>333959</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>407780</t>
+          <t>402331</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>212430</t>
+          <t>215004</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>266801</t>
+          <t>268931</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>563179</t>
+          <t>561914</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>652589</t>
+          <t>653848</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>598752</t>
+          <t>598347</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>679504</t>
+          <t>681670</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>292931</t>
+          <t>291263</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>355893</t>
+          <t>356031</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>903152</t>
+          <t>904954</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1014274</t>
+          <t>1013420</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la edad, en cuartiles, de inicio en el consumo de tabaco en 2023</t>
+          <t>Población según la edad, en cuartiles, de inicio en el consumo de tabaco en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24935</t>
+          <t>25604</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46420</t>
+          <t>46799</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22870</t>
+          <t>22821</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38819</t>
+          <t>38398</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52730</t>
+          <t>51620</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79925</t>
+          <t>79081</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44458</t>
+          <t>45216</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71111</t>
+          <t>74044</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48396</t>
+          <t>47156</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68288</t>
+          <t>66696</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98533</t>
+          <t>98015</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>133622</t>
+          <t>134896</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>74151</t>
+          <t>71866</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>105454</t>
+          <t>103462</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42202</t>
+          <t>42116</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63504</t>
+          <t>62766</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>120463</t>
+          <t>119949</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>158508</t>
+          <t>159051</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,66%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93805</t>
+          <t>94013</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126655</t>
+          <t>129998</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21581</t>
+          <t>21973</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39275</t>
+          <t>39714</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119926</t>
+          <t>121852</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159510</t>
+          <t>161168</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15895</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>102590</t>
+          <t>100022</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36074</t>
+          <t>35692</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>56289</t>
+          <t>57110</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>46042</t>
+          <t>42239</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>149984</t>
+          <t>148167</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35103</t>
+          <t>40049</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>178876</t>
+          <t>185346</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63286</t>
+          <t>62833</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88192</t>
+          <t>87889</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86104</t>
+          <t>87723</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>256762</t>
+          <t>256448</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,73%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>165702</t>
+          <t>166161</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>538781</t>
+          <t>531647</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70469</t>
+          <t>69821</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97952</t>
+          <t>99358</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>254228</t>
+          <t>254779</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>666136</t>
+          <t>680848</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>76,27%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43333</t>
+          <t>42179</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>205030</t>
+          <t>206751</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45045</t>
+          <t>45466</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68408</t>
+          <t>68823</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>87032</t>
+          <t>81419</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>251603</t>
+          <t>254213</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48125</t>
+          <t>47676</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>79601</t>
+          <t>79619</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46147</t>
+          <t>46036</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68973</t>
+          <t>69289</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>100783</t>
+          <t>99036</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>139371</t>
+          <t>138740</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>84420</t>
+          <t>84312</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>123458</t>
+          <t>125087</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54065</t>
+          <t>54247</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78595</t>
+          <t>79559</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>144195</t>
+          <t>143746</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>193526</t>
+          <t>193536</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53323</t>
+          <t>53151</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85812</t>
+          <t>86215</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31980</t>
+          <t>32393</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54382</t>
+          <t>53495</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90253</t>
+          <t>90838</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>128608</t>
+          <t>130793</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89100</t>
+          <t>88927</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>130216</t>
+          <t>129937</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50911</t>
+          <t>50784</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>77527</t>
+          <t>76251</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>150935</t>
+          <t>148200</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198335</t>
+          <t>201225</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,44%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65333</t>
+          <t>65452</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>97660</t>
+          <t>95639</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61946</t>
+          <t>64280</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88501</t>
+          <t>88547</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>135626</t>
+          <t>135907</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>176367</t>
+          <t>174757</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>82204</t>
+          <t>81963</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>118773</t>
+          <t>117048</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>86880</t>
+          <t>88331</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>115556</t>
+          <t>115995</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>179747</t>
+          <t>176452</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>227022</t>
+          <t>220940</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>66628</t>
+          <t>65033</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>98442</t>
+          <t>96664</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44870</t>
+          <t>44869</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>67354</t>
+          <t>68697</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>116121</t>
+          <t>116201</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>154546</t>
+          <t>155451</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>130177</t>
+          <t>129964</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>167700</t>
+          <t>169236</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>72475</t>
+          <t>73284</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>99871</t>
+          <t>99119</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>210503</t>
+          <t>211718</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>258606</t>
+          <t>258860</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>132634</t>
+          <t>137893</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>285318</t>
+          <t>284512</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>186967</t>
+          <t>187328</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>232521</t>
+          <t>231062</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>322436</t>
+          <t>310826</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>498272</t>
+          <t>498919</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>220265</t>
+          <t>215927</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>439549</t>
+          <t>437312</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>273207</t>
+          <t>275331</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>324155</t>
+          <t>326591</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>476863</t>
+          <t>481216</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>744333</t>
+          <t>753192</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>387749</t>
+          <t>389819</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1011789</t>
+          <t>1033221</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>206947</t>
+          <t>206587</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>253934</t>
+          <t>257547</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>616118</t>
+          <t>618185</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1315560</t>
+          <t>1340553</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>50,71%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>298145</t>
+          <t>296898</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>583493</t>
+          <t>587979</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>212404</t>
+          <t>210736</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>259085</t>
+          <t>259962</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>523840</t>
+          <t>509845</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>815602</t>
+          <t>811062</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q23_tabaco_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15806</t>
+          <t>17188</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35644</t>
+          <t>36186</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20784</t>
+          <t>20732</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40224</t>
+          <t>39815</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42123</t>
+          <t>41359</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69637</t>
+          <t>70497</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102206</t>
+          <t>102673</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>137099</t>
+          <t>137884</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50918</t>
+          <t>50685</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76556</t>
+          <t>75889</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>161002</t>
+          <t>160844</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>206545</t>
+          <t>207244</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,8%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65061</t>
+          <t>63753</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94164</t>
+          <t>96333</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28160</t>
+          <t>27526</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49739</t>
+          <t>50943</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>98571</t>
+          <t>99072</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>137473</t>
+          <t>136949</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>128022</t>
+          <t>126667</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>166107</t>
+          <t>165714</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37284</t>
+          <t>37130</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60812</t>
+          <t>60343</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172019</t>
+          <t>171526</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>216577</t>
+          <t>218387</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,84%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54167</t>
+          <t>52291</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88214</t>
+          <t>86716</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51287</t>
+          <t>50860</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80226</t>
+          <t>79814</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>112427</t>
+          <t>114507</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>155975</t>
+          <t>157534</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>149145</t>
+          <t>147930</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>195677</t>
+          <t>191360</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87416</t>
+          <t>87119</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>120067</t>
+          <t>120200</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>250906</t>
+          <t>245427</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>304941</t>
+          <t>300423</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>37,77%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88552</t>
+          <t>89573</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126330</t>
+          <t>127381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36342</t>
+          <t>37638</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60605</t>
+          <t>62691</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133384</t>
+          <t>133947</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>178644</t>
+          <t>178138</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>149576</t>
+          <t>151434</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>192403</t>
+          <t>193935</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47746</t>
+          <t>48666</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75172</t>
+          <t>78571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>204357</t>
+          <t>207748</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>260444</t>
+          <t>258960</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25194</t>
+          <t>25637</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48384</t>
+          <t>47400</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36377</t>
+          <t>35896</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59938</t>
+          <t>60590</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66051</t>
+          <t>67237</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99232</t>
+          <t>102120</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93081</t>
+          <t>94124</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>130878</t>
+          <t>127837</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51183</t>
+          <t>51430</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>76613</t>
+          <t>77162</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>154165</t>
+          <t>153461</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>197773</t>
+          <t>199020</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,81%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59191</t>
+          <t>59351</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90206</t>
+          <t>93737</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22212</t>
+          <t>22498</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42314</t>
+          <t>42009</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88742</t>
+          <t>87086</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>125899</t>
+          <t>124382</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106666</t>
+          <t>109438</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>145608</t>
+          <t>145005</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38423</t>
+          <t>38678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61795</t>
+          <t>62542</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>154934</t>
+          <t>154686</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>202638</t>
+          <t>198815</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43277</t>
+          <t>44271</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72596</t>
+          <t>73058</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60170</t>
+          <t>60031</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>92545</t>
+          <t>92402</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111678</t>
+          <t>111293</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>153564</t>
+          <t>153006</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>133443</t>
+          <t>131554</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>172938</t>
+          <t>170385</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>94240</t>
+          <t>93854</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>127821</t>
+          <t>129440</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>236140</t>
+          <t>237071</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>288482</t>
+          <t>290334</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,76%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>97919</t>
+          <t>97096</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>132929</t>
+          <t>133939</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48537</t>
+          <t>47759</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>76239</t>
+          <t>75656</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>152612</t>
+          <t>154890</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>200601</t>
+          <t>200344</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>146065</t>
+          <t>146702</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>185527</t>
+          <t>187543</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>84640</t>
+          <t>86174</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>118799</t>
+          <t>117773</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>242129</t>
+          <t>241593</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>293664</t>
+          <t>294654</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>159419</t>
+          <t>161911</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>215021</t>
+          <t>214988</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>189889</t>
+          <t>191529</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>243171</t>
+          <t>241927</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>367237</t>
+          <t>366343</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>441739</t>
+          <t>443958</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>513862</t>
+          <t>513599</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>591289</t>
+          <t>589328</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>308552</t>
+          <t>308950</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>369448</t>
+          <t>370274</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>844605</t>
+          <t>844359</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>942683</t>
+          <t>939954</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>340382</t>
+          <t>339895</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>408777</t>
+          <t>408919</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>154881</t>
+          <t>155785</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>205037</t>
+          <t>204075</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>511341</t>
+          <t>512424</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>592782</t>
+          <t>597150</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>572225</t>
+          <t>567441</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>650850</t>
+          <t>653171</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>234941</t>
+          <t>234847</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>292311</t>
+          <t>290074</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>820550</t>
+          <t>821881</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>919160</t>
+          <t>921289</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51366</t>
+          <t>51158</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82293</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36060</t>
+          <t>36591</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62160</t>
+          <t>62491</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93198</t>
+          <t>94448</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>134839</t>
+          <t>133530</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102345</t>
+          <t>100747</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>138958</t>
+          <t>139547</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64058</t>
+          <t>64123</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>93120</t>
+          <t>94329</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>175718</t>
+          <t>174094</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>222299</t>
+          <t>223371</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,78%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67859</t>
+          <t>65298</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99404</t>
+          <t>100295</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35073</t>
+          <t>35485</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60710</t>
+          <t>61761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>108990</t>
+          <t>108322</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>150367</t>
+          <t>150556</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>154318</t>
+          <t>154913</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>195050</t>
+          <t>198345</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35354</t>
+          <t>33990</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62019</t>
+          <t>60483</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>196289</t>
+          <t>196499</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>246641</t>
+          <t>247753</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,47%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89258</t>
+          <t>88996</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>130611</t>
+          <t>129030</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>76671</t>
+          <t>75357</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>110737</t>
+          <t>110532</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>175462</t>
+          <t>172904</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>229868</t>
+          <t>228894</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>147245</t>
+          <t>147188</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>192903</t>
+          <t>193610</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>107114</t>
+          <t>107475</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>144015</t>
+          <t>143649</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>264320</t>
+          <t>265973</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>324717</t>
+          <t>324374</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>114711</t>
+          <t>113193</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>158939</t>
+          <t>156981</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41251</t>
+          <t>40568</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70100</t>
+          <t>68115</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163184</t>
+          <t>164844</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>216041</t>
+          <t>215078</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>187774</t>
+          <t>186525</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>236477</t>
+          <t>235845</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>88398</t>
+          <t>88582</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>124953</t>
+          <t>125812</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>288916</t>
+          <t>288094</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>348961</t>
+          <t>351043</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,06%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63126</t>
+          <t>63278</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99860</t>
+          <t>102143</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59410</t>
+          <t>59241</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>92658</t>
+          <t>92221</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>130935</t>
+          <t>132562</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>180926</t>
+          <t>183036</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>121647</t>
+          <t>122440</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>164819</t>
+          <t>163564</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71899</t>
+          <t>72714</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>104546</t>
+          <t>105092</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>203684</t>
+          <t>200883</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>257007</t>
+          <t>256622</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54678</t>
+          <t>54155</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85467</t>
+          <t>85549</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52477</t>
+          <t>51876</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84597</t>
+          <t>84196</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>115871</t>
+          <t>113559</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159540</t>
+          <t>156235</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>140090</t>
+          <t>141356</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>186096</t>
+          <t>186734</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75870</t>
+          <t>75570</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>109818</t>
+          <t>112666</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>229154</t>
+          <t>228825</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>283735</t>
+          <t>284397</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,64%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>64952</t>
+          <t>66400</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>100618</t>
+          <t>101922</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>74270</t>
+          <t>72852</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>107753</t>
+          <t>106860</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>147666</t>
+          <t>149954</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>197895</t>
+          <t>200404</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>147598</t>
+          <t>146658</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>190623</t>
+          <t>188919</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>105117</t>
+          <t>108396</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>143452</t>
+          <t>143663</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>262848</t>
+          <t>261904</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>319318</t>
+          <t>319554</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,62%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>74010</t>
+          <t>73226</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>110034</t>
+          <t>108188</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>51437</t>
+          <t>50474</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>80273</t>
+          <t>80577</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>132300</t>
+          <t>131794</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>178394</t>
+          <t>177657</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>163478</t>
+          <t>163594</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>209228</t>
+          <t>208910</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>99272</t>
+          <t>100623</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>137946</t>
+          <t>138346</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>274290</t>
+          <t>276717</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>334724</t>
+          <t>334786</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>296710</t>
+          <t>298689</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>370892</t>
+          <t>373634</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>272069</t>
+          <t>275705</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>337775</t>
+          <t>338105</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>594325</t>
+          <t>595997</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>692506</t>
+          <t>691867</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>554835</t>
+          <t>556101</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>641369</t>
+          <t>640312</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>380444</t>
+          <t>381882</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>450557</t>
+          <t>450424</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>960857</t>
+          <t>958211</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1071043</t>
+          <t>1069118</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>340351</t>
+          <t>338180</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>411138</t>
+          <t>411033</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>205790</t>
+          <t>206060</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>261481</t>
+          <t>262678</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>564998</t>
+          <t>560145</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>656947</t>
+          <t>652065</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>689918</t>
+          <t>691164</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>780342</t>
+          <t>779873</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>331337</t>
+          <t>331478</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>402629</t>
+          <t>400047</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1041138</t>
+          <t>1045128</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1156243</t>
+          <t>1159739</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50848</t>
+          <t>49277</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80910</t>
+          <t>80833</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46618</t>
+          <t>45923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73313</t>
+          <t>73262</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>106004</t>
+          <t>103311</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>145898</t>
+          <t>144156</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80952</t>
+          <t>79727</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>115435</t>
+          <t>114692</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62164</t>
+          <t>63837</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91344</t>
+          <t>90987</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>151947</t>
+          <t>149938</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>196251</t>
+          <t>196738</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,7%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44671</t>
+          <t>43767</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>73210</t>
+          <t>73032</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22035</t>
+          <t>22032</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42770</t>
+          <t>41466</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>72471</t>
+          <t>71375</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>106234</t>
+          <t>105127</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>138385</t>
+          <t>140613</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>177533</t>
+          <t>180378</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44860</t>
+          <t>45547</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71514</t>
+          <t>70755</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>193616</t>
+          <t>193849</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>241212</t>
+          <t>241804</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,19%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79397</t>
+          <t>80248</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>117146</t>
+          <t>116454</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63883</t>
+          <t>63320</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>94371</t>
+          <t>95358</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>151949</t>
+          <t>151148</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>200405</t>
+          <t>200192</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>100186</t>
+          <t>97673</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>140456</t>
+          <t>138355</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88648</t>
+          <t>87633</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>124049</t>
+          <t>123139</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>197617</t>
+          <t>197009</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>248786</t>
+          <t>252249</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89431</t>
+          <t>88137</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128114</t>
+          <t>126263</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56566</t>
+          <t>55497</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86291</t>
+          <t>86586</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>157401</t>
+          <t>155663</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>203637</t>
+          <t>201906</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>179353</t>
+          <t>176516</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>224542</t>
+          <t>221964</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>87708</t>
+          <t>88600</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>122807</t>
+          <t>122685</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>276150</t>
+          <t>274642</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>334882</t>
+          <t>334747</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50925</t>
+          <t>52178</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>82078</t>
+          <t>81400</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52132</t>
+          <t>51833</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80586</t>
+          <t>80027</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111987</t>
+          <t>112670</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153967</t>
+          <t>153657</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>98386</t>
+          <t>98383</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136872</t>
+          <t>136021</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>79621</t>
+          <t>78905</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>111230</t>
+          <t>110660</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>188925</t>
+          <t>188059</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>236363</t>
+          <t>239104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,12%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95380</t>
+          <t>94492</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>134717</t>
+          <t>133840</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52885</t>
+          <t>53859</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82022</t>
+          <t>82330</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>155637</t>
+          <t>157162</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>206051</t>
+          <t>203738</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>114634</t>
+          <t>115647</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>154095</t>
+          <t>155849</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53171</t>
+          <t>52988</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>81100</t>
+          <t>81094</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>176837</t>
+          <t>173255</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>226097</t>
+          <t>224130</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49832</t>
+          <t>49530</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80159</t>
+          <t>77749</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79363</t>
+          <t>77515</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112552</t>
+          <t>114870</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>137928</t>
+          <t>136143</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>184383</t>
+          <t>182341</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>122300</t>
+          <t>122928</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>160280</t>
+          <t>164423</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>88583</t>
+          <t>88197</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>121611</t>
+          <t>123566</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>218659</t>
+          <t>219128</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>272476</t>
+          <t>273417</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75350</t>
+          <t>73269</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>110335</t>
+          <t>107966</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>57064</t>
+          <t>57780</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>88642</t>
+          <t>89888</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140937</t>
+          <t>140500</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>189147</t>
+          <t>186289</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>126893</t>
+          <t>127685</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>168044</t>
+          <t>167577</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78041</t>
+          <t>79495</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>111330</t>
+          <t>113077</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>216843</t>
+          <t>216303</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>270505</t>
+          <t>269446</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,28%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>260349</t>
+          <t>260933</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>325449</t>
+          <t>324088</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>267788</t>
+          <t>269181</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>330423</t>
+          <t>332065</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>549075</t>
+          <t>541386</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>632826</t>
+          <t>634607</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>435364</t>
+          <t>434453</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>511439</t>
+          <t>512964</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>350950</t>
+          <t>351228</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>417655</t>
+          <t>414916</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>807519</t>
+          <t>805992</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>903699</t>
+          <t>901498</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>333959</t>
+          <t>330679</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>402331</t>
+          <t>401875</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>215004</t>
+          <t>213339</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>268931</t>
+          <t>266703</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>561914</t>
+          <t>565113</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>653848</t>
+          <t>653757</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>598347</t>
+          <t>596422</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>681670</t>
+          <t>678993</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>291263</t>
+          <t>295955</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>356031</t>
+          <t>357459</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>904954</t>
+          <t>908851</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1013420</t>
+          <t>1015207</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,69%</t>
         </is>
       </c>
     </row>
@@ -9959,32 +9959,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>34476</t>
+          <t>37407</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25604</t>
+          <t>28199</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46799</t>
+          <t>50745</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,32 +9994,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>30410</t>
+          <t>31646</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22821</t>
+          <t>23971</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38398</t>
+          <t>39540</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>64887</t>
+          <t>69053</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51620</t>
+          <t>55905</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79081</t>
+          <t>83191</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57576</t>
+          <t>64753</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45216</t>
+          <t>49590</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74044</t>
+          <t>81980</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56987</t>
+          <t>61692</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47156</t>
+          <t>50523</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66696</t>
+          <t>72937</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>114563</t>
+          <t>126445</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98015</t>
+          <t>108110</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>134896</t>
+          <t>146072</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87561</t>
+          <t>93727</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71866</t>
+          <t>76301</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>103462</t>
+          <t>112347</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51517</t>
+          <t>56162</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42116</t>
+          <t>45413</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62766</t>
+          <t>67787</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>139079</t>
+          <t>149889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>119949</t>
+          <t>128849</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>159051</t>
+          <t>171852</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>110328</t>
+          <t>116540</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94013</t>
+          <t>97895</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>129998</t>
+          <t>133710</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29969</t>
+          <t>30324</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21973</t>
+          <t>21864</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39714</t>
+          <t>41293</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>140297</t>
+          <t>146864</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>121852</t>
+          <t>128088</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>161168</t>
+          <t>166788</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>289941</t>
+          <t>312428</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>289941</t>
+          <t>312428</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>289941</t>
+          <t>312428</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>168884</t>
+          <t>179823</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>168884</t>
+          <t>179823</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>168884</t>
+          <t>179823</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>458825</t>
+          <t>492251</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>458825</t>
+          <t>492251</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>458825</t>
+          <t>492251</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,32 +10528,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55338</t>
+          <t>55315</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18847</t>
+          <t>41888</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100022</t>
+          <t>71019</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10563,32 +10563,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45596</t>
+          <t>49316</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35692</t>
+          <t>39993</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57110</t>
+          <t>60881</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>100934</t>
+          <t>104630</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>42239</t>
+          <t>86648</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>148167</t>
+          <t>122741</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>104239</t>
+          <t>118201</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40049</t>
+          <t>99224</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>185346</t>
+          <t>140168</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>75318</t>
+          <t>81332</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62833</t>
+          <t>67996</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87889</t>
+          <t>96681</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>179556</t>
+          <t>199532</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87723</t>
+          <t>175378</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>256448</t>
+          <t>221864</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>352750</t>
+          <t>121393</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>166161</t>
+          <t>101368</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531647</t>
+          <t>141002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,32 +10789,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>82684</t>
+          <t>90193</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69821</t>
+          <t>76014</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99358</t>
+          <t>106175</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>435434</t>
+          <t>211585</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>254779</t>
+          <t>189412</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>680848</t>
+          <t>235637</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>120616</t>
+          <t>126822</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42179</t>
+          <t>108532</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>206751</t>
+          <t>148008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56117</t>
+          <t>61208</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45466</t>
+          <t>49747</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68823</t>
+          <t>76066</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>176733</t>
+          <t>188030</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>81419</t>
+          <t>167044</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>254213</t>
+          <t>216529</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>30,77%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>632943</t>
+          <t>421730</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>632943</t>
+          <t>421730</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>632943</t>
+          <t>421730</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>259714</t>
+          <t>282048</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>259714</t>
+          <t>282048</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>259714</t>
+          <t>282048</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>892657</t>
+          <t>703778</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>892657</t>
+          <t>703778</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>892657</t>
+          <t>703778</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11097,32 +11097,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>62272</t>
+          <t>71834</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47676</t>
+          <t>55940</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>79619</t>
+          <t>90376</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>56944</t>
+          <t>67719</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46036</t>
+          <t>55322</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69289</t>
+          <t>80110</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>119216</t>
+          <t>139553</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>99036</t>
+          <t>119269</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>138740</t>
+          <t>162097</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>25,71%</t>
         </is>
       </c>
     </row>
@@ -11210,32 +11210,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>102607</t>
+          <t>113045</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>84312</t>
+          <t>94673</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>125087</t>
+          <t>132736</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65864</t>
+          <t>71300</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54247</t>
+          <t>58459</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>79559</t>
+          <t>84309</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>168471</t>
+          <t>184345</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>143746</t>
+          <t>159475</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>193536</t>
+          <t>211496</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,55%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>67110</t>
+          <t>74436</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53151</t>
+          <t>58405</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86215</t>
+          <t>93207</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>41664</t>
+          <t>47488</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32393</t>
+          <t>36369</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53495</t>
+          <t>61052</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>108774</t>
+          <t>121924</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90838</t>
+          <t>101286</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130793</t>
+          <t>143951</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>108303</t>
+          <t>117424</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88927</t>
+          <t>96563</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129937</t>
+          <t>137243</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>63087</t>
+          <t>67199</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50784</t>
+          <t>54795</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76251</t>
+          <t>82437</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>171391</t>
+          <t>184624</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>148200</t>
+          <t>162004</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>201225</t>
+          <t>211375</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>340292</t>
+          <t>376740</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>340292</t>
+          <t>376740</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>340292</t>
+          <t>376740</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>227559</t>
+          <t>253706</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>227559</t>
+          <t>253706</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>227559</t>
+          <t>253706</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>567852</t>
+          <t>630446</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>567852</t>
+          <t>630446</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>567852</t>
+          <t>630446</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>79240</t>
+          <t>82301</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65452</t>
+          <t>66766</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95639</t>
+          <t>99416</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>75267</t>
+          <t>81891</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64280</t>
+          <t>67762</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88547</t>
+          <t>95577</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>154507</t>
+          <t>164191</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>135907</t>
+          <t>144503</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>174757</t>
+          <t>187074</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>98117</t>
+          <t>108744</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>81963</t>
+          <t>90592</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>117048</t>
+          <t>127934</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>101113</t>
+          <t>110054</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>88331</t>
+          <t>94913</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>115995</t>
+          <t>125442</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>199229</t>
+          <t>218797</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>176452</t>
+          <t>195451</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>220940</t>
+          <t>244128</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>31,46%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>80365</t>
+          <t>86294</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>65033</t>
+          <t>71017</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>96664</t>
+          <t>104258</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,17 +11927,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>55287</t>
+          <t>59261</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44869</t>
+          <t>48378</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>68697</t>
+          <t>71817</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>135652</t>
+          <t>145555</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>116201</t>
+          <t>126715</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>155451</t>
+          <t>169659</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>148721</t>
+          <t>158217</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>129964</t>
+          <t>138060</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>169236</t>
+          <t>177271</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>85887</t>
+          <t>89132</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>73284</t>
+          <t>76002</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>99119</t>
+          <t>104453</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>234609</t>
+          <t>247349</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>211718</t>
+          <t>221454</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>258860</t>
+          <t>271979</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,05%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>406443</t>
+          <t>435556</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>406443</t>
+          <t>435556</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>406443</t>
+          <t>435556</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>317554</t>
+          <t>340337</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>317554</t>
+          <t>340337</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>317554</t>
+          <t>340337</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>723997</t>
+          <t>775893</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>723997</t>
+          <t>775893</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>723997</t>
+          <t>775893</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>231327</t>
+          <t>246857</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>137893</t>
+          <t>217666</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>284512</t>
+          <t>280276</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>208217</t>
+          <t>230571</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>187328</t>
+          <t>208966</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>231062</t>
+          <t>256951</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>439543</t>
+          <t>477427</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>310826</t>
+          <t>445190</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>498919</t>
+          <t>518838</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>362538</t>
+          <t>404742</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>215927</t>
+          <t>368375</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>437312</t>
+          <t>442212</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>299282</t>
+          <t>324378</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>275331</t>
+          <t>295306</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>326591</t>
+          <t>353459</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>661820</t>
+          <t>729120</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>481216</t>
+          <t>687877</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>753192</t>
+          <t>776023</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>29,82%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>587786</t>
+          <t>375851</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>389819</t>
+          <t>339581</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1033221</t>
+          <t>412626</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>231153</t>
+          <t>253103</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>206587</t>
+          <t>225624</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>257547</t>
+          <t>280458</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>818939</t>
+          <t>628954</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>618185</t>
+          <t>585637</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1340553</t>
+          <t>669765</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>487969</t>
+          <t>519004</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>296898</t>
+          <t>480345</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>587979</t>
+          <t>557676</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>235060</t>
+          <t>247863</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>210736</t>
+          <t>223224</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>259962</t>
+          <t>273858</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>723029</t>
+          <t>766867</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>509845</t>
+          <t>720426</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>811062</t>
+          <t>809577</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1669620</t>
+          <t>1546454</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1669620</t>
+          <t>1546454</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1669620</t>
+          <t>1546454</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>973711</t>
+          <t>1055914</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>973711</t>
+          <t>1055914</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>973711</t>
+          <t>1055914</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2643331</t>
+          <t>2602368</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2643331</t>
+          <t>2602368</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2643331</t>
+          <t>2602368</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
